--- a/A1.xlsx
+++ b/A1.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kirill\2) ДОМ\19) WM PYTHON\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kirill\1) ONELIGHT APP\WM_calculations\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E71EE1D6-1064-4DAF-BA7C-BAC36F56A9CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D121AD2-27D0-450E-901F-9A700F54FF5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C101"/>
+  <dimension ref="A1:C130"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="10.6640625" customWidth="1"/>
@@ -1468,6 +1468,325 @@
         <v>0</v>
       </c>
     </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A102">
+        <v>101</v>
+      </c>
+      <c r="B102">
+        <v>1</v>
+      </c>
+      <c r="C102">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A103">
+        <v>102</v>
+      </c>
+      <c r="B103">
+        <v>1</v>
+      </c>
+      <c r="C103">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A104">
+        <v>103</v>
+      </c>
+      <c r="B104">
+        <v>1</v>
+      </c>
+      <c r="C104">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A105">
+        <v>104</v>
+      </c>
+      <c r="B105">
+        <v>1</v>
+      </c>
+      <c r="C105">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A106">
+        <v>105</v>
+      </c>
+      <c r="B106">
+        <v>1</v>
+      </c>
+      <c r="C106">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A107">
+        <v>106</v>
+      </c>
+      <c r="B107">
+        <v>1</v>
+      </c>
+      <c r="C107">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A108">
+        <v>107</v>
+      </c>
+      <c r="B108">
+        <v>1</v>
+      </c>
+      <c r="C108">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A109">
+        <v>108</v>
+      </c>
+      <c r="B109">
+        <v>1</v>
+      </c>
+      <c r="C109">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A110">
+        <v>109</v>
+      </c>
+      <c r="B110">
+        <v>1</v>
+      </c>
+      <c r="C110">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A111">
+        <v>110</v>
+      </c>
+      <c r="B111">
+        <v>1</v>
+      </c>
+      <c r="C111">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A112">
+        <v>111</v>
+      </c>
+      <c r="B112">
+        <v>1</v>
+      </c>
+      <c r="C112">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A113">
+        <v>112</v>
+      </c>
+      <c r="B113">
+        <v>1</v>
+      </c>
+      <c r="C113">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A114">
+        <v>113</v>
+      </c>
+      <c r="B114">
+        <v>1</v>
+      </c>
+      <c r="C114">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A115">
+        <v>114</v>
+      </c>
+      <c r="B115">
+        <v>1</v>
+      </c>
+      <c r="C115">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A116">
+        <v>115</v>
+      </c>
+      <c r="B116">
+        <v>1</v>
+      </c>
+      <c r="C116">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A117">
+        <v>116</v>
+      </c>
+      <c r="B117">
+        <v>1</v>
+      </c>
+      <c r="C117">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A118">
+        <v>117</v>
+      </c>
+      <c r="B118">
+        <v>1</v>
+      </c>
+      <c r="C118">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A119">
+        <v>118</v>
+      </c>
+      <c r="B119">
+        <v>1</v>
+      </c>
+      <c r="C119">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A120">
+        <v>119</v>
+      </c>
+      <c r="B120">
+        <v>1</v>
+      </c>
+      <c r="C120">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A121">
+        <v>120</v>
+      </c>
+      <c r="B121">
+        <v>1</v>
+      </c>
+      <c r="C121">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A122">
+        <v>121</v>
+      </c>
+      <c r="B122">
+        <v>1</v>
+      </c>
+      <c r="C122">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A123">
+        <v>122</v>
+      </c>
+      <c r="B123">
+        <v>1</v>
+      </c>
+      <c r="C123">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A124">
+        <v>123</v>
+      </c>
+      <c r="B124">
+        <v>1</v>
+      </c>
+      <c r="C124">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A125">
+        <v>124</v>
+      </c>
+      <c r="B125">
+        <v>1</v>
+      </c>
+      <c r="C125">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A126">
+        <v>125</v>
+      </c>
+      <c r="B126">
+        <v>1</v>
+      </c>
+      <c r="C126">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A127">
+        <v>126</v>
+      </c>
+      <c r="B127">
+        <v>1</v>
+      </c>
+      <c r="C127">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A128">
+        <v>127</v>
+      </c>
+      <c r="B128">
+        <v>1</v>
+      </c>
+      <c r="C128">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A129">
+        <v>128</v>
+      </c>
+      <c r="B129">
+        <v>1</v>
+      </c>
+      <c r="C129">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A130">
+        <v>129</v>
+      </c>
+      <c r="B130">
+        <v>1</v>
+      </c>
+      <c r="C130">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/A1.xlsx
+++ b/A1.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kirill\1) ONELIGHT APP\WM_calculations\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D121AD2-27D0-450E-901F-9A700F54FF5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA6C44B7-D5C0-418D-8247-A3FB11EF9327}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
     <t>power</t>
   </si>
   <si>
-    <t>kill_count</t>
+    <t>inf_kills</t>
   </si>
 </sst>
 </file>

--- a/A1.xlsx
+++ b/A1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kirill\1) ONELIGHT APP\WM_calculations\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA6C44B7-D5C0-418D-8247-A3FB11EF9327}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A40AF18-B6C5-4BFD-ACE1-8E7479DFF7C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <t>sol_id</t>
   </si>
@@ -34,6 +34,9 @@
   </si>
   <si>
     <t>inf_kills</t>
+  </si>
+  <si>
+    <t>apc_kills</t>
   </si>
 </sst>
 </file>
@@ -351,13 +354,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C130"/>
+  <dimension ref="A1:D130"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="10.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -367,8 +370,11 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -378,8 +384,11 @@
       <c r="C2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -389,8 +398,11 @@
       <c r="C3">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -400,8 +412,11 @@
       <c r="C4">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
@@ -411,8 +426,11 @@
       <c r="C5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
@@ -422,8 +440,11 @@
       <c r="C6">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
@@ -433,8 +454,11 @@
       <c r="C7">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
@@ -444,8 +468,11 @@
       <c r="C8">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
@@ -455,8 +482,11 @@
       <c r="C9">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
@@ -466,8 +496,11 @@
       <c r="C10">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
@@ -477,8 +510,11 @@
       <c r="C11">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>11</v>
       </c>
@@ -488,8 +524,11 @@
       <c r="C12">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>12</v>
       </c>
@@ -499,8 +538,11 @@
       <c r="C13">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>13</v>
       </c>
@@ -510,8 +552,11 @@
       <c r="C14">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>14</v>
       </c>
@@ -521,8 +566,11 @@
       <c r="C15">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>15</v>
       </c>
@@ -532,8 +580,11 @@
       <c r="C16">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>16</v>
       </c>
@@ -543,8 +594,11 @@
       <c r="C17">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>17</v>
       </c>
@@ -554,8 +608,11 @@
       <c r="C18">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>18</v>
       </c>
@@ -565,8 +622,11 @@
       <c r="C19">
         <v>0</v>
       </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>19</v>
       </c>
@@ -576,8 +636,11 @@
       <c r="C20">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>20</v>
       </c>
@@ -587,8 +650,11 @@
       <c r="C21">
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>21</v>
       </c>
@@ -598,8 +664,11 @@
       <c r="C22">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>22</v>
       </c>
@@ -609,8 +678,11 @@
       <c r="C23">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>23</v>
       </c>
@@ -620,8 +692,11 @@
       <c r="C24">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>24</v>
       </c>
@@ -631,8 +706,11 @@
       <c r="C25">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>25</v>
       </c>
@@ -642,8 +720,11 @@
       <c r="C26">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>26</v>
       </c>
@@ -653,8 +734,11 @@
       <c r="C27">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>27</v>
       </c>
@@ -664,8 +748,11 @@
       <c r="C28">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>28</v>
       </c>
@@ -675,8 +762,11 @@
       <c r="C29">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>29</v>
       </c>
@@ -686,8 +776,11 @@
       <c r="C30">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>30</v>
       </c>
@@ -697,8 +790,11 @@
       <c r="C31">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>31</v>
       </c>
@@ -708,8 +804,11 @@
       <c r="C32">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>32</v>
       </c>
@@ -719,8 +818,11 @@
       <c r="C33">
         <v>0</v>
       </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>33</v>
       </c>
@@ -730,8 +832,11 @@
       <c r="C34">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>34</v>
       </c>
@@ -741,8 +846,11 @@
       <c r="C35">
         <v>0</v>
       </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>35</v>
       </c>
@@ -752,8 +860,11 @@
       <c r="C36">
         <v>0</v>
       </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>36</v>
       </c>
@@ -763,8 +874,11 @@
       <c r="C37">
         <v>0</v>
       </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>37</v>
       </c>
@@ -774,8 +888,11 @@
       <c r="C38">
         <v>0</v>
       </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>38</v>
       </c>
@@ -785,8 +902,11 @@
       <c r="C39">
         <v>0</v>
       </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>39</v>
       </c>
@@ -796,8 +916,11 @@
       <c r="C40">
         <v>0</v>
       </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>40</v>
       </c>
@@ -807,8 +930,11 @@
       <c r="C41">
         <v>0</v>
       </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>41</v>
       </c>
@@ -818,8 +944,11 @@
       <c r="C42">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>42</v>
       </c>
@@ -829,8 +958,11 @@
       <c r="C43">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>43</v>
       </c>
@@ -840,8 +972,11 @@
       <c r="C44">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>44</v>
       </c>
@@ -851,8 +986,11 @@
       <c r="C45">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>45</v>
       </c>
@@ -862,8 +1000,11 @@
       <c r="C46">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>46</v>
       </c>
@@ -873,8 +1014,11 @@
       <c r="C47">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>47</v>
       </c>
@@ -884,8 +1028,11 @@
       <c r="C48">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>48</v>
       </c>
@@ -895,8 +1042,11 @@
       <c r="C49">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>49</v>
       </c>
@@ -906,8 +1056,11 @@
       <c r="C50">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>50</v>
       </c>
@@ -917,8 +1070,11 @@
       <c r="C51">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>51</v>
       </c>
@@ -928,8 +1084,11 @@
       <c r="C52">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>52</v>
       </c>
@@ -939,8 +1098,11 @@
       <c r="C53">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>53</v>
       </c>
@@ -950,8 +1112,11 @@
       <c r="C54">
         <v>0</v>
       </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>54</v>
       </c>
@@ -961,8 +1126,11 @@
       <c r="C55">
         <v>0</v>
       </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>55</v>
       </c>
@@ -972,8 +1140,11 @@
       <c r="C56">
         <v>0</v>
       </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>56</v>
       </c>
@@ -983,8 +1154,11 @@
       <c r="C57">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>57</v>
       </c>
@@ -994,8 +1168,11 @@
       <c r="C58">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>58</v>
       </c>
@@ -1005,8 +1182,11 @@
       <c r="C59">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>59</v>
       </c>
@@ -1016,8 +1196,11 @@
       <c r="C60">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>60</v>
       </c>
@@ -1027,8 +1210,11 @@
       <c r="C61">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>61</v>
       </c>
@@ -1038,8 +1224,11 @@
       <c r="C62">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>62</v>
       </c>
@@ -1049,8 +1238,11 @@
       <c r="C63">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>63</v>
       </c>
@@ -1060,8 +1252,11 @@
       <c r="C64">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>64</v>
       </c>
@@ -1071,8 +1266,11 @@
       <c r="C65">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>65</v>
       </c>
@@ -1082,8 +1280,11 @@
       <c r="C66">
         <v>0</v>
       </c>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>66</v>
       </c>
@@ -1093,8 +1294,11 @@
       <c r="C67">
         <v>0</v>
       </c>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>67</v>
       </c>
@@ -1104,8 +1308,11 @@
       <c r="C68">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A69">
         <v>68</v>
       </c>
@@ -1115,8 +1322,11 @@
       <c r="C69">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>69</v>
       </c>
@@ -1126,8 +1336,11 @@
       <c r="C70">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>70</v>
       </c>
@@ -1137,8 +1350,11 @@
       <c r="C71">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A72">
         <v>71</v>
       </c>
@@ -1148,8 +1364,11 @@
       <c r="C72">
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A73">
         <v>72</v>
       </c>
@@ -1159,8 +1378,11 @@
       <c r="C73">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>73</v>
       </c>
@@ -1170,8 +1392,11 @@
       <c r="C74">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A75">
         <v>74</v>
       </c>
@@ -1181,8 +1406,11 @@
       <c r="C75">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A76">
         <v>75</v>
       </c>
@@ -1192,8 +1420,11 @@
       <c r="C76">
         <v>0</v>
       </c>
-    </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A77">
         <v>76</v>
       </c>
@@ -1203,8 +1434,11 @@
       <c r="C77">
         <v>0</v>
       </c>
-    </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A78">
         <v>77</v>
       </c>
@@ -1214,8 +1448,11 @@
       <c r="C78">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A79">
         <v>78</v>
       </c>
@@ -1225,8 +1462,11 @@
       <c r="C79">
         <v>0</v>
       </c>
-    </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A80">
         <v>79</v>
       </c>
@@ -1236,8 +1476,11 @@
       <c r="C80">
         <v>0</v>
       </c>
-    </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A81">
         <v>80</v>
       </c>
@@ -1247,8 +1490,11 @@
       <c r="C81">
         <v>0</v>
       </c>
-    </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A82">
         <v>81</v>
       </c>
@@ -1258,8 +1504,11 @@
       <c r="C82">
         <v>0</v>
       </c>
-    </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A83">
         <v>82</v>
       </c>
@@ -1269,8 +1518,11 @@
       <c r="C83">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A84">
         <v>83</v>
       </c>
@@ -1280,8 +1532,11 @@
       <c r="C84">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A85">
         <v>84</v>
       </c>
@@ -1291,8 +1546,11 @@
       <c r="C85">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A86">
         <v>85</v>
       </c>
@@ -1302,8 +1560,11 @@
       <c r="C86">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A87">
         <v>86</v>
       </c>
@@ -1313,8 +1574,11 @@
       <c r="C87">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A88">
         <v>87</v>
       </c>
@@ -1324,8 +1588,11 @@
       <c r="C88">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A89">
         <v>88</v>
       </c>
@@ -1335,8 +1602,11 @@
       <c r="C89">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A90">
         <v>89</v>
       </c>
@@ -1346,8 +1616,11 @@
       <c r="C90">
         <v>0</v>
       </c>
-    </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A91">
         <v>90</v>
       </c>
@@ -1357,8 +1630,11 @@
       <c r="C91">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A92">
         <v>91</v>
       </c>
@@ -1368,8 +1644,11 @@
       <c r="C92">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A93">
         <v>92</v>
       </c>
@@ -1379,8 +1658,11 @@
       <c r="C93">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A94">
         <v>93</v>
       </c>
@@ -1390,8 +1672,11 @@
       <c r="C94">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A95">
         <v>94</v>
       </c>
@@ -1401,8 +1686,11 @@
       <c r="C95">
         <v>0</v>
       </c>
-    </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A96">
         <v>95</v>
       </c>
@@ -1412,8 +1700,11 @@
       <c r="C96">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A97">
         <v>96</v>
       </c>
@@ -1423,8 +1714,11 @@
       <c r="C97">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A98">
         <v>97</v>
       </c>
@@ -1434,8 +1728,11 @@
       <c r="C98">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A99">
         <v>98</v>
       </c>
@@ -1445,8 +1742,11 @@
       <c r="C99">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A100">
         <v>99</v>
       </c>
@@ -1456,8 +1756,11 @@
       <c r="C100">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A101">
         <v>100</v>
       </c>
@@ -1467,8 +1770,11 @@
       <c r="C101">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D101">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A102">
         <v>101</v>
       </c>
@@ -1478,8 +1784,11 @@
       <c r="C102">
         <v>0</v>
       </c>
-    </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D102">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A103">
         <v>102</v>
       </c>
@@ -1489,8 +1798,11 @@
       <c r="C103">
         <v>0</v>
       </c>
-    </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D103">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A104">
         <v>103</v>
       </c>
@@ -1500,8 +1812,11 @@
       <c r="C104">
         <v>0</v>
       </c>
-    </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D104">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A105">
         <v>104</v>
       </c>
@@ -1511,8 +1826,11 @@
       <c r="C105">
         <v>0</v>
       </c>
-    </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D105">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A106">
         <v>105</v>
       </c>
@@ -1522,8 +1840,11 @@
       <c r="C106">
         <v>0</v>
       </c>
-    </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D106">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A107">
         <v>106</v>
       </c>
@@ -1533,8 +1854,11 @@
       <c r="C107">
         <v>0</v>
       </c>
-    </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D107">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A108">
         <v>107</v>
       </c>
@@ -1544,8 +1868,11 @@
       <c r="C108">
         <v>0</v>
       </c>
-    </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D108">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A109">
         <v>108</v>
       </c>
@@ -1555,8 +1882,11 @@
       <c r="C109">
         <v>0</v>
       </c>
-    </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D109">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A110">
         <v>109</v>
       </c>
@@ -1566,8 +1896,11 @@
       <c r="C110">
         <v>0</v>
       </c>
-    </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D110">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A111">
         <v>110</v>
       </c>
@@ -1577,8 +1910,11 @@
       <c r="C111">
         <v>0</v>
       </c>
-    </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D111">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A112">
         <v>111</v>
       </c>
@@ -1588,8 +1924,11 @@
       <c r="C112">
         <v>0</v>
       </c>
-    </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D112">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A113">
         <v>112</v>
       </c>
@@ -1599,8 +1938,11 @@
       <c r="C113">
         <v>0</v>
       </c>
-    </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D113">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A114">
         <v>113</v>
       </c>
@@ -1610,8 +1952,11 @@
       <c r="C114">
         <v>0</v>
       </c>
-    </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D114">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A115">
         <v>114</v>
       </c>
@@ -1621,8 +1966,11 @@
       <c r="C115">
         <v>0</v>
       </c>
-    </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D115">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A116">
         <v>115</v>
       </c>
@@ -1632,8 +1980,11 @@
       <c r="C116">
         <v>0</v>
       </c>
-    </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D116">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A117">
         <v>116</v>
       </c>
@@ -1643,8 +1994,11 @@
       <c r="C117">
         <v>0</v>
       </c>
-    </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D117">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A118">
         <v>117</v>
       </c>
@@ -1654,8 +2008,11 @@
       <c r="C118">
         <v>0</v>
       </c>
-    </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D118">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A119">
         <v>118</v>
       </c>
@@ -1665,8 +2022,11 @@
       <c r="C119">
         <v>0</v>
       </c>
-    </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D119">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A120">
         <v>119</v>
       </c>
@@ -1676,8 +2036,11 @@
       <c r="C120">
         <v>0</v>
       </c>
-    </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D120">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A121">
         <v>120</v>
       </c>
@@ -1687,8 +2050,11 @@
       <c r="C121">
         <v>0</v>
       </c>
-    </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D121">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A122">
         <v>121</v>
       </c>
@@ -1698,8 +2064,11 @@
       <c r="C122">
         <v>0</v>
       </c>
-    </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D122">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A123">
         <v>122</v>
       </c>
@@ -1709,8 +2078,11 @@
       <c r="C123">
         <v>0</v>
       </c>
-    </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D123">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A124">
         <v>123</v>
       </c>
@@ -1720,8 +2092,11 @@
       <c r="C124">
         <v>0</v>
       </c>
-    </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D124">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A125">
         <v>124</v>
       </c>
@@ -1731,8 +2106,11 @@
       <c r="C125">
         <v>0</v>
       </c>
-    </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D125">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A126">
         <v>125</v>
       </c>
@@ -1742,8 +2120,11 @@
       <c r="C126">
         <v>0</v>
       </c>
-    </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D126">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A127">
         <v>126</v>
       </c>
@@ -1753,8 +2134,11 @@
       <c r="C127">
         <v>0</v>
       </c>
-    </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D127">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A128">
         <v>127</v>
       </c>
@@ -1764,8 +2148,11 @@
       <c r="C128">
         <v>0</v>
       </c>
-    </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D128">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A129">
         <v>128</v>
       </c>
@@ -1775,8 +2162,11 @@
       <c r="C129">
         <v>0</v>
       </c>
-    </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D129">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A130">
         <v>129</v>
       </c>
@@ -1784,6 +2174,9 @@
         <v>1</v>
       </c>
       <c r="C130">
+        <v>0</v>
+      </c>
+      <c r="D130">
         <v>0</v>
       </c>
     </row>
